--- a/2excel.xlxs..xlsx
+++ b/2excel.xlxs..xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11591" uniqueCount="4324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11597" uniqueCount="4329">
   <si>
     <t>OrderID</t>
   </si>
@@ -12998,6 +12998,21 @@
   </si>
   <si>
     <t>HEART</t>
+  </si>
+  <si>
+    <t>shyam</t>
+  </si>
+  <si>
+    <t>cd</t>
+  </si>
+  <si>
+    <t>read</t>
+  </si>
+  <si>
+    <t>tm</t>
+  </si>
+  <si>
+    <t>how</t>
   </si>
 </sst>
 </file>
@@ -69233,7 +69248,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -69366,6 +69381,58 @@
         <v>10</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>238</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4324</v>
+      </c>
+      <c r="C6">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4325</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4326</v>
+      </c>
+      <c r="F6">
+        <v>432</v>
+      </c>
+      <c r="G6">
+        <v>500</v>
+      </c>
+      <c r="H6">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>239</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4311</v>
+      </c>
+      <c r="C7">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>4327</v>
+      </c>
+      <c r="E7" t="s">
+        <v>4328</v>
+      </c>
+      <c r="F7">
+        <v>567</v>
+      </c>
+      <c r="G7">
+        <v>700</v>
+      </c>
+      <c r="H7">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2excel.xlxs..xlsx
+++ b/2excel.xlxs..xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11597" uniqueCount="4329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11600" uniqueCount="4332">
   <si>
     <t>OrderID</t>
   </si>
@@ -13013,6 +13013,15 @@
   </si>
   <si>
     <t>how</t>
+  </si>
+  <si>
+    <t>don</t>
+  </si>
+  <si>
+    <t>3h</t>
+  </si>
+  <si>
+    <t>minke</t>
   </si>
 </sst>
 </file>
@@ -69248,7 +69257,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -69433,6 +69442,32 @@
         <v>54</v>
       </c>
     </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>720</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4329</v>
+      </c>
+      <c r="C8">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>4330</v>
+      </c>
+      <c r="E8" t="s">
+        <v>4331</v>
+      </c>
+      <c r="F8">
+        <v>780</v>
+      </c>
+      <c r="G8">
+        <v>300</v>
+      </c>
+      <c r="H8">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
